--- a/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
+++ b/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE5DBBA-E7BA-4A08-83FB-785C22223BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663F348-E824-49E9-B1E2-2B511BA4949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1329,7 +1329,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S14</t>
+    <t>システム機能設計書_サンプル_S26</t>
   </si>
   <si>
     <t>B5</t>
@@ -3420,7 +3420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95CEC5E3-01EA-420F-8809-5CC4B4D881C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463DB1CD-2869-4130-8F01-36FE749694ED}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4937,23 +4937,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{E7BE6BEE-925F-4F47-946C-92B2704A0F8B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{FBE1A021-E2DD-489F-ABF7-2815DC370902}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{2084B58D-D1D8-48D4-9404-5DE002473B2F}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{B536EF07-E722-4A09-944E-33BC4900428E}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{FCF2B0C1-E10B-446C-A835-505DB436989E}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{9E17B8BF-47B0-4784-AE50-1C8216965CF7}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{33666D71-9329-4628-8DC0-90C44A072D3A}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{13D59B04-C793-4F68-ACA0-99AB90692B59}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{757EE079-EE96-4D1C-BA7E-F8F47893DCDF}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{6A0FD9A6-FDBF-4AD9-BA41-A0CE99CD00B0}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{99B56810-2821-40C3-8760-2DF0D594E4B5}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{6A4F09E0-4DFD-4E61-9F16-336947A5AB86}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{D85D311C-3695-4ABB-A930-7040A8950AC9}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{F5435669-4C16-46AA-9874-9624670371ED}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{34E56944-1A33-443B-8D1B-EB2187C0D81B}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{71F99892-F3A4-4AC2-BBEA-F8ECEE31EBBA}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{CFECC20D-87CB-4A93-BEFB-07EA6313EA6E}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{85516C35-EF9A-46A9-8358-6E677107438E}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{45329672-902F-4BAA-A8D4-8627D8FAF2E9}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{C365A3CE-574E-47B1-B356-6BB9A4B5AEFA}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{28815E1C-709B-4B7A-AF1E-3A07E6A6B952}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{CF26257E-DC35-40CD-925F-81B152CE4B7B}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{A1264CB9-AD6E-40CC-9ADB-DCC817F9ABCE}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{003E4CA7-70CE-4C27-AA9B-AE0335BED7F0}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{803EF682-F254-416A-A957-F94CFBE85B36}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{FDB7DF19-73CF-4CD2-9507-2FE14DE250C6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>

--- a/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
+++ b/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
@@ -5,15 +5,15 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663F348-E824-49E9-B1E2-2B511BA4949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DD04EC-7594-45E0-97A2-A6FB3EBFEB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="レビュー結果1回目" sheetId="11" r:id="rId1"/>
+    <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
     <sheet name="表紙" sheetId="1" r:id="rId2"/>
     <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
     <sheet name="目次" sheetId="3" r:id="rId4"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$N$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$K$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
@@ -175,77 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E66" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:g
-疑問点・確認の指摘例（カテゴリg）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E67" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:h
-改善要望の指摘例（カテゴリh）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E68" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:i
-仕様変更の指摘例（カテゴリi）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E69" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:j
-テスト項目漏れの指摘例（カテゴリj）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E70" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:k
-テスト漏れの指摘例（カテゴリk）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -259,26 +189,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E71" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="ＭＳ 明朝"/>
-            <family val="1"/>
-            <charset val="128"/>
-          </rPr>
-          <t>山田　太郎:l
-その他の指摘例（カテゴリl）。</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="322">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1329,7 +1245,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S26</t>
+    <t>システム機能設計書_サンプル_S25</t>
   </si>
   <si>
     <t>B5</t>
@@ -1401,108 +1317,6 @@
   </si>
   <si>
     <t>記述誤りの指摘例（カテゴリf）。</t>
-  </si>
-  <si>
-    <t>g</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>h</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>i</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>j</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>k</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>l</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>91_疑問点、確認</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>92_改善要望</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>93_仕様変更</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>94_テスト項目漏れ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>95_テスト漏れ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>96_その他</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>E66</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>疑問点・確認の指摘例（カテゴリg）。</t>
-  </si>
-  <si>
-    <t>E67</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>改善要望の指摘例（カテゴリh）。</t>
-  </si>
-  <si>
-    <t>E68</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>仕様変更の指摘例（カテゴリi）。</t>
-  </si>
-  <si>
-    <t>E69</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>テスト項目漏れの指摘例（カテゴリj）。</t>
-  </si>
-  <si>
-    <t>E70</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>テスト漏れの指摘例（カテゴリk）。</t>
-  </si>
-  <si>
-    <t>E71</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>その他の指摘例（カテゴリl）。</t>
   </si>
 </sst>
 </file>
@@ -3420,31 +3234,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463DB1CD-2869-4130-8F01-36FE749694ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{522FC151-6765-4840-8E68-6EF745E84406}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="262"/>
-    <col min="2" max="14" width="17.6640625" style="262" customWidth="1"/>
-    <col min="15" max="26" width="4.5" style="262" customWidth="1"/>
-    <col min="27" max="27" width="98.1640625" style="262" customWidth="1"/>
-    <col min="28" max="16384" width="9.33203125" style="262"/>
+    <col min="2" max="11" width="17.6640625" style="262" customWidth="1"/>
+    <col min="12" max="17" width="4.5" style="262" customWidth="1"/>
+    <col min="18" max="18" width="98.1640625" style="262" customWidth="1"/>
+    <col min="19" max="20" width="4.5" style="262" customWidth="1"/>
+    <col min="21" max="21" width="98.1640625" style="262" customWidth="1"/>
+    <col min="22" max="16384" width="9.33203125" style="262"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A1" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="O1" s="263"/>
-      <c r="AA1" s="264" t="s">
+      <c r="L1" s="263"/>
+      <c r="R1" s="264" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A2" s="262" t="s">
         <v>267</v>
       </c>
@@ -3455,9 +3271,9 @@
       <c r="G2" s="266"/>
       <c r="H2" s="266"/>
       <c r="I2" s="267"/>
-      <c r="O2" s="263"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.15">
+      <c r="L2" s="263"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="268" t="s">
         <v>269</v>
       </c>
@@ -3479,7 +3295,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4" s="271" t="s">
         <v>300</v>
       </c>
@@ -3503,12 +3319,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" s="261" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B7" s="276" t="s">
         <v>277</v>
       </c>
@@ -3527,26 +3343,8 @@
       <c r="G7" s="270" t="s">
         <v>282</v>
       </c>
-      <c r="H7" s="270" t="s">
-        <v>322</v>
-      </c>
-      <c r="I7" s="270" t="s">
-        <v>323</v>
-      </c>
-      <c r="J7" s="270" t="s">
-        <v>324</v>
-      </c>
-      <c r="K7" s="270" t="s">
-        <v>325</v>
-      </c>
-      <c r="L7" s="270" t="s">
-        <v>326</v>
-      </c>
-      <c r="M7" s="270" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="27" x14ac:dyDescent="0.15">
+    </row>
+    <row r="8" spans="1:18" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="269" t="s">
         <v>283</v>
       </c>
@@ -3568,197 +3366,104 @@
       <c r="G8" s="277" t="s">
         <v>289</v>
       </c>
-      <c r="H8" s="277" t="s">
-        <v>328</v>
-      </c>
-      <c r="I8" s="277" t="s">
-        <v>329</v>
-      </c>
-      <c r="J8" s="277" t="s">
-        <v>330</v>
-      </c>
-      <c r="K8" s="277" t="s">
-        <v>331</v>
-      </c>
-      <c r="L8" s="277" t="s">
-        <v>332</v>
-      </c>
-      <c r="M8" s="277" t="s">
-        <v>333</v>
-      </c>
-      <c r="N8" s="279" t="s">
+      <c r="H8" s="279" t="s">
         <v>290</v>
       </c>
+      <c r="I8" s="280"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="280"/>
+      <c r="L8" s="280"/>
+      <c r="M8" s="280"/>
+      <c r="N8" s="280"/>
       <c r="O8" s="280"/>
       <c r="P8" s="280"/>
       <c r="Q8" s="280"/>
-      <c r="R8" s="280"/>
-      <c r="S8" s="280"/>
-      <c r="T8" s="280"/>
-      <c r="U8" s="280"/>
-      <c r="V8" s="280"/>
-      <c r="W8" s="280"/>
-      <c r="X8" s="280"/>
-      <c r="Y8" s="280"/>
-      <c r="Z8" s="280"/>
-      <c r="AA8" s="280"/>
-      <c r="AB8" s="280"/>
-      <c r="AC8" s="280"/>
-      <c r="AD8" s="280"/>
-      <c r="AE8" s="280"/>
-      <c r="AF8" s="280"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A9" s="269" t="s">
         <v>291</v>
       </c>
       <c r="B9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,O15:O27)=0,"",SUMIF($K15:$K27,$A9,O15:O27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,L15:L21)=0,"",SUMIF($K15:$K21,$A9,L15:L21))</f>
         <v/>
       </c>
       <c r="C9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,P15:P27)=0,"",SUMIF($K15:$K27,$A9,P15:P27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,M15:M21)=0,"",SUMIF($K15:$K21,$A9,M15:M21))</f>
         <v/>
       </c>
       <c r="D9" s="281">
-        <f>IF(SUMIF($K15:$K27,$A9,Q15:Q27)=0,"",SUMIF($K15:$K27,$A9,Q15:Q27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,N15:N21)=0,"",SUMIF($K15:$K21,$A9,N15:N21))</f>
         <v>1</v>
       </c>
       <c r="E9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,R15:R27)=0,"",SUMIF($K15:$K27,$A9,R15:R27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,O15:O21)=0,"",SUMIF($K15:$K21,$A9,O15:O21))</f>
         <v/>
       </c>
       <c r="F9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,S15:S27)=0,"",SUMIF($K15:$K27,$A9,S15:S27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,P15:P21)=0,"",SUMIF($K15:$K21,$A9,P15:P21))</f>
         <v/>
       </c>
       <c r="G9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,T15:T27)=0,"",SUMIF($K15:$K27,$A9,T15:T27))</f>
+        <f>IF(SUMIF($K15:$K21,$A9,Q15:Q21)=0,"",SUMIF($K15:$K21,$A9,Q15:Q21))</f>
         <v/>
       </c>
-      <c r="H9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,U15:U27)=0,"",SUMIF($K15:$K27,$A9,U15:U27))</f>
-        <v/>
-      </c>
-      <c r="I9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,V15:V27)=0,"",SUMIF($K15:$K27,$A9,V15:V27))</f>
-        <v/>
-      </c>
-      <c r="J9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,W15:W27)=0,"",SUMIF($K15:$K27,$A9,W15:W27))</f>
-        <v/>
-      </c>
-      <c r="K9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,X15:X27)=0,"",SUMIF($K15:$K27,$A9,X15:X27))</f>
-        <v/>
-      </c>
-      <c r="L9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,Y15:Y27)=0,"",SUMIF($K15:$K27,$A9,Y15:Y27))</f>
-        <v/>
-      </c>
-      <c r="M9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A9,Z15:Z27)=0,"",SUMIF($K15:$K27,$A9,Z15:Z27))</f>
-        <v/>
-      </c>
-      <c r="N9" s="282">
-        <f>SUM(B9:M9)</f>
+      <c r="H9" s="282">
+        <f>SUM(B9:G9)</f>
         <v>1</v>
       </c>
+      <c r="I9" s="261"/>
+      <c r="J9" s="261"/>
+      <c r="K9" s="261"/>
+      <c r="L9" s="261"/>
+      <c r="M9" s="261"/>
+      <c r="N9" s="261"/>
       <c r="O9" s="261"/>
       <c r="P9" s="261"/>
       <c r="Q9" s="261"/>
-      <c r="R9" s="261"/>
-      <c r="S9" s="261"/>
-      <c r="T9" s="261"/>
-      <c r="U9" s="261"/>
-      <c r="V9" s="261"/>
-      <c r="W9" s="261"/>
-      <c r="X9" s="261"/>
-      <c r="Y9" s="261"/>
-      <c r="Z9" s="261"/>
-      <c r="AA9" s="261"/>
-      <c r="AB9" s="261"/>
-      <c r="AC9" s="261"/>
-      <c r="AD9" s="261"/>
-      <c r="AE9" s="261"/>
-      <c r="AF9" s="261"/>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A10" s="269" t="s">
         <v>292</v>
       </c>
       <c r="B10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,O15:O27)=0,"",SUMIF($K15:$K27,$A10,O15:O27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,L15:L21)=0,"",SUMIF($K15:$K21,$A10,L15:L21))</f>
         <v>1</v>
       </c>
       <c r="C10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,P15:P27)=0,"",SUMIF($K15:$K27,$A10,P15:P27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,M15:M21)=0,"",SUMIF($K15:$K21,$A10,M15:M21))</f>
         <v>1</v>
       </c>
       <c r="D10" s="281" t="str">
-        <f>IF(SUMIF($K15:$K27,$A10,Q15:Q27)=0,"",SUMIF($K15:$K27,$A10,Q15:Q27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,N15:N21)=0,"",SUMIF($K15:$K21,$A10,N15:N21))</f>
         <v/>
       </c>
       <c r="E10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,R15:R27)=0,"",SUMIF($K15:$K27,$A10,R15:R27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,O15:O21)=0,"",SUMIF($K15:$K21,$A10,O15:O21))</f>
         <v>1</v>
       </c>
       <c r="F10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,S15:S27)=0,"",SUMIF($K15:$K27,$A10,S15:S27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,P15:P21)=0,"",SUMIF($K15:$K21,$A10,P15:P21))</f>
         <v>1</v>
       </c>
       <c r="G10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,T15:T27)=0,"",SUMIF($K15:$K27,$A10,T15:T27))</f>
+        <f>IF(SUMIF($K15:$K21,$A10,Q15:Q21)=0,"",SUMIF($K15:$K21,$A10,Q15:Q21))</f>
         <v>1</v>
       </c>
-      <c r="H10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,U15:U27)=0,"",SUMIF($K15:$K27,$A10,U15:U27))</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,V15:V27)=0,"",SUMIF($K15:$K27,$A10,V15:V27))</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,W15:W27)=0,"",SUMIF($K15:$K27,$A10,W15:W27))</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,X15:X27)=0,"",SUMIF($K15:$K27,$A10,X15:X27))</f>
-        <v>1</v>
-      </c>
-      <c r="L10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,Y15:Y27)=0,"",SUMIF($K15:$K27,$A10,Y15:Y27))</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="281">
-        <f>IF(SUMIF($K15:$K27,$A10,Z15:Z27)=0,"",SUMIF($K15:$K27,$A10,Z15:Z27))</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="282">
-        <f>SUM(B10:M10)</f>
-        <v>11</v>
-      </c>
+      <c r="H10" s="282">
+        <f>SUM(B10:G10)</f>
+        <v>5</v>
+      </c>
+      <c r="I10" s="261"/>
+      <c r="J10" s="261"/>
+      <c r="K10" s="261"/>
+      <c r="L10" s="261"/>
+      <c r="M10" s="261"/>
+      <c r="N10" s="261"/>
       <c r="O10" s="261"/>
       <c r="P10" s="261"/>
       <c r="Q10" s="261"/>
-      <c r="R10" s="261"/>
-      <c r="S10" s="261"/>
-      <c r="T10" s="261"/>
-      <c r="U10" s="261"/>
-      <c r="V10" s="261"/>
-      <c r="W10" s="261"/>
-      <c r="X10" s="261"/>
-      <c r="Y10" s="261"/>
-      <c r="Z10" s="261"/>
-      <c r="AA10" s="261"/>
-      <c r="AB10" s="261"/>
-      <c r="AC10" s="261"/>
-      <c r="AD10" s="261"/>
-      <c r="AE10" s="261"/>
-      <c r="AF10" s="261"/>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A11" s="283" t="s">
         <v>290</v>
       </c>
@@ -3767,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="284">
-        <f t="shared" ref="C11:M11" si="0">SUM(C9:C10)</f>
+        <f t="shared" ref="C11:G11" si="0">SUM(C9:C10)</f>
         <v>1</v>
       </c>
       <c r="D11" s="284">
@@ -3787,35 +3492,11 @@
         <v>1</v>
       </c>
       <c r="H11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="284">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N11" s="284">
-        <f>SUM(B11:M11)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.15">
+        <f>SUM(B11:G11)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A12" s="261"/>
       <c r="B12" s="285"/>
       <c r="C12" s="285"/>
@@ -3827,11 +3508,8 @@
       <c r="I12" s="285"/>
       <c r="J12" s="285"/>
       <c r="K12" s="285"/>
-      <c r="L12" s="285"/>
-      <c r="M12" s="285"/>
-      <c r="N12" s="285"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A13" s="286" t="s">
         <v>293</v>
       </c>
@@ -3839,22 +3517,16 @@
       <c r="C13" s="287"/>
       <c r="D13" s="287"/>
       <c r="F13" s="287"/>
-      <c r="O13" s="263" t="s">
+      <c r="L13" s="263" t="s">
         <v>294</v>
       </c>
+      <c r="M13" s="263"/>
+      <c r="N13" s="263"/>
+      <c r="O13" s="263"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="263"/>
-      <c r="R13" s="263"/>
-      <c r="S13" s="263"/>
-      <c r="T13" s="263"/>
-      <c r="U13" s="263"/>
-      <c r="V13" s="263"/>
-      <c r="W13" s="263"/>
-      <c r="X13" s="263"/>
-      <c r="Y13" s="263"/>
-      <c r="Z13" s="263"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.15">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A14" s="288" t="s">
         <v>295</v>
       </c>
@@ -3878,44 +3550,26 @@
       <c r="K14" s="293" t="s">
         <v>283</v>
       </c>
+      <c r="L14" s="294" t="s">
+        <v>277</v>
+      </c>
+      <c r="M14" s="294" t="s">
+        <v>278</v>
+      </c>
+      <c r="N14" s="294" t="s">
+        <v>279</v>
+      </c>
       <c r="O14" s="294" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P14" s="294" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q14" s="294" t="s">
-        <v>279</v>
-      </c>
-      <c r="R14" s="294" t="s">
-        <v>280</v>
-      </c>
-      <c r="S14" s="294" t="s">
-        <v>281</v>
-      </c>
-      <c r="T14" s="294" t="s">
         <v>282</v>
       </c>
-      <c r="U14" s="294" t="s">
-        <v>322</v>
-      </c>
-      <c r="V14" s="294" t="s">
-        <v>323</v>
-      </c>
-      <c r="W14" s="294" t="s">
-        <v>324</v>
-      </c>
-      <c r="X14" s="294" t="s">
-        <v>325</v>
-      </c>
-      <c r="Y14" s="294" t="s">
-        <v>326</v>
-      </c>
-      <c r="Z14" s="294" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="40.5" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:18" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A15" s="272" t="s">
         <v>38</v>
       </c>
@@ -3939,9 +3593,21 @@
       <c r="K15" s="272" t="s">
         <v>305</v>
       </c>
+      <c r="L15" s="295">
+        <f t="shared" ref="L15:Q21" si="1">IF($D15=L$14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O15" s="295">
-        <f t="shared" ref="O15:Z27" si="1">IF($D15=O$14,1,0)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="P15" s="295">
         <f t="shared" si="1"/>
@@ -3951,50 +3617,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="296" t="str">
+      <c r="R15" s="296" t="str">
         <f>IF(E15&lt;&gt;"",E15,"")</f>
         <v>レビュー指摘コメントの例。
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
 ※レビュー日時を書く場合はコロンの直後に*を書く。</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A16" s="272" t="s">
         <v>38</v>
       </c>
@@ -4018,62 +3648,38 @@
       <c r="K16" s="272" t="s">
         <v>305</v>
       </c>
+      <c r="L16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P16" s="295">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="296" t="str">
+      <c r="R16" s="296" t="str">
         <f>IF(E16&lt;&gt;"",E16,"")</f>
         <v>対応内容の例。
 ---
 対応内容はデリミタ（---）の後に記入する。</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:18" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A17" s="272" t="s">
         <v>38</v>
       </c>
@@ -4097,6 +3703,18 @@
       <c r="K17" s="272" t="s">
         <v>312</v>
       </c>
+      <c r="L17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="O17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4107,45 +3725,9 @@
       </c>
       <c r="Q17" s="295">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="R17" s="295">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="296" t="str">
+      <c r="R17" s="296" t="str">
         <f>IF(E17&lt;&gt;"",E17,"")</f>
         <v>対応内容を確認し、指摘をクローズする例。
 ---
@@ -4154,7 +3736,7 @@
 08/02山田 済</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A18" s="272" t="s">
         <v>38</v>
       </c>
@@ -4178,9 +3760,21 @@
       <c r="K18" s="272" t="s">
         <v>305</v>
       </c>
+      <c r="L18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O18" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="295">
         <f t="shared" si="1"/>
@@ -4190,48 +3784,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R18" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="296" t="str">
+      <c r="R18" s="296" t="str">
         <f>IF(E18&lt;&gt;"",E18,"")</f>
         <v>機能・仕様誤りの指摘例（カテゴリd）。</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A19" s="272" t="s">
         <v>38</v>
       </c>
@@ -4255,60 +3813,36 @@
       <c r="K19" s="272" t="s">
         <v>305</v>
       </c>
+      <c r="L19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O19" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P19" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="296" t="str">
+      <c r="R19" s="296" t="str">
         <f>IF(E19&lt;&gt;"",E19,"")</f>
         <v>設計・ドキュメント規約違反の指摘例（カテゴリe）。</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A20" s="272" t="s">
         <v>38</v>
       </c>
@@ -4332,6 +3866,18 @@
       <c r="K20" s="272" t="s">
         <v>305</v>
       </c>
+      <c r="L20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="O20" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4342,72 +3888,36 @@
       </c>
       <c r="Q20" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="295">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="U20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="296" t="str">
+      <c r="R20" s="296" t="str">
         <f>IF(E20&lt;&gt;"",E20,"")</f>
         <v>記述誤りの指摘例（カテゴリf）。</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A21" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="297" t="s">
-        <v>334</v>
-      </c>
-      <c r="C21" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D21" s="272" t="s">
-        <v>335</v>
-      </c>
-      <c r="E21" s="271" t="s">
-        <v>336</v>
-      </c>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A21" s="272"/>
+      <c r="B21" s="272"/>
+      <c r="C21" s="272"/>
+      <c r="D21" s="272"/>
+      <c r="E21" s="271"/>
       <c r="F21" s="271"/>
       <c r="G21" s="271"/>
       <c r="H21" s="271"/>
       <c r="I21" s="271"/>
       <c r="J21" s="271"/>
-      <c r="K21" s="272" t="s">
-        <v>305</v>
+      <c r="K21" s="272"/>
+      <c r="L21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="O21" s="295">
         <f t="shared" si="1"/>
@@ -4421,505 +3931,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="296" t="str">
+      <c r="R21" s="296" t="str">
         <f>IF(E21&lt;&gt;"",E21,"")</f>
-        <v>疑問点・確認の指摘例（カテゴリg）。</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A22" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="297" t="s">
-        <v>337</v>
-      </c>
-      <c r="C22" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D22" s="272" t="s">
-        <v>338</v>
-      </c>
-      <c r="E22" s="271" t="s">
-        <v>339</v>
-      </c>
-      <c r="F22" s="271"/>
-      <c r="G22" s="271"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-      <c r="K22" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="O22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="W22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA22" s="296" t="str">
-        <f>IF(E22&lt;&gt;"",E22,"")</f>
-        <v>改善要望の指摘例（カテゴリh）。</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A23" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="297" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D23" s="272" t="s">
-        <v>341</v>
-      </c>
-      <c r="E23" s="271" t="s">
-        <v>342</v>
-      </c>
-      <c r="F23" s="271"/>
-      <c r="G23" s="271"/>
-      <c r="H23" s="271"/>
-      <c r="I23" s="271"/>
-      <c r="J23" s="271"/>
-      <c r="K23" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="O23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W23" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="X23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA23" s="296" t="str">
-        <f>IF(E23&lt;&gt;"",E23,"")</f>
-        <v>仕様変更の指摘例（カテゴリi）。</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A24" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="297" t="s">
-        <v>343</v>
-      </c>
-      <c r="C24" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D24" s="272" t="s">
-        <v>344</v>
-      </c>
-      <c r="E24" s="271" t="s">
-        <v>345</v>
-      </c>
-      <c r="F24" s="271"/>
-      <c r="G24" s="271"/>
-      <c r="H24" s="271"/>
-      <c r="I24" s="271"/>
-      <c r="J24" s="271"/>
-      <c r="K24" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="O24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA24" s="296" t="str">
-        <f>IF(E24&lt;&gt;"",E24,"")</f>
-        <v>テスト項目漏れの指摘例（カテゴリj）。</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A25" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="297" t="s">
-        <v>346</v>
-      </c>
-      <c r="C25" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="272" t="s">
-        <v>347</v>
-      </c>
-      <c r="E25" s="271" t="s">
-        <v>348</v>
-      </c>
-      <c r="F25" s="271"/>
-      <c r="G25" s="271"/>
-      <c r="H25" s="271"/>
-      <c r="I25" s="271"/>
-      <c r="J25" s="271"/>
-      <c r="K25" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="O25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Z25" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA25" s="296" t="str">
-        <f>IF(E25&lt;&gt;"",E25,"")</f>
-        <v>テスト漏れの指摘例（カテゴリk）。</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A26" s="272" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="297" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="272" t="s">
-        <v>302</v>
-      </c>
-      <c r="D26" s="272" t="s">
-        <v>350</v>
-      </c>
-      <c r="E26" s="271" t="s">
-        <v>351</v>
-      </c>
-      <c r="F26" s="271"/>
-      <c r="G26" s="271"/>
-      <c r="H26" s="271"/>
-      <c r="I26" s="271"/>
-      <c r="J26" s="271"/>
-      <c r="K26" s="272" t="s">
-        <v>305</v>
-      </c>
-      <c r="O26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="AA26" s="296" t="str">
-        <f>IF(E26&lt;&gt;"",E26,"")</f>
-        <v>その他の指摘例（カテゴリl）。</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A27" s="272"/>
-      <c r="B27" s="272"/>
-      <c r="C27" s="272"/>
-      <c r="D27" s="272"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="271"/>
-      <c r="H27" s="271"/>
-      <c r="I27" s="271"/>
-      <c r="J27" s="271"/>
-      <c r="K27" s="272"/>
-      <c r="O27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="296" t="str">
-        <f>IF(E27&lt;&gt;"",E27,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="E22:J22"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="E25:J25"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="E27:J27"/>
+  <mergeCells count="9">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E15:J15"/>
@@ -4931,32 +3949,26 @@
     <mergeCell ref="E21:J21"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
-  <conditionalFormatting sqref="A15:K27">
+  <conditionalFormatting sqref="A15:K21">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$K15="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{FBE1A021-E2DD-489F-ABF7-2815DC370902}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K21" xr:uid="{6E56FA6A-CA48-4A70-8E37-7684E7188C3C}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{34E56944-1A33-443B-8D1B-EB2187C0D81B}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{71F99892-F3A4-4AC2-BBEA-F8ECEE31EBBA}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{CFECC20D-87CB-4A93-BEFB-07EA6313EA6E}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{85516C35-EF9A-46A9-8358-6E677107438E}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{45329672-902F-4BAA-A8D4-8627D8FAF2E9}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{C365A3CE-574E-47B1-B356-6BB9A4B5AEFA}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{28815E1C-709B-4B7A-AF1E-3A07E6A6B952}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{CF26257E-DC35-40CD-925F-81B152CE4B7B}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{A1264CB9-AD6E-40CC-9ADB-DCC817F9ABCE}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{003E4CA7-70CE-4C27-AA9B-AE0335BED7F0}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{803EF682-F254-416A-A957-F94CFBE85B36}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{FDB7DF19-73CF-4CD2-9507-2FE14DE250C6}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{9B74B046-36F0-4244-870F-AA45C50FDBA4}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{35ECCE01-B1B4-436C-BBB4-850C2F1820F4}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{9697448F-645A-41FB-AA3F-4313B4171D87}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{C9647F5F-F163-4499-88A9-FE5C8EC41F54}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{446BD414-9F72-4680-85DB-437C59B7F4B8}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{6F0B7F15-88AA-41F1-9DA5-B98FEA05983C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>

--- a/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
+++ b/doctool/test/auto/scenario26/システム機能設計書_サンプル_S26_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DD04EC-7594-45E0-97A2-A6FB3EBFEB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4097B46F-A4CD-4CB9-A51B-0DA164890890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
@@ -1245,7 +1245,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S25</t>
+    <t>システム機能設計書_サンプル_S26</t>
   </si>
   <si>
     <t>B5</t>
@@ -3234,7 +3234,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{522FC151-6765-4840-8E68-6EF745E84406}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A30B5B2-9480-4568-9BDC-8E35E72B6843}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3955,17 +3955,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K21" xr:uid="{6E56FA6A-CA48-4A70-8E37-7684E7188C3C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K21" xr:uid="{274AF5E0-0E64-407D-B161-A005E9E42AFD}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{9B74B046-36F0-4244-870F-AA45C50FDBA4}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{35ECCE01-B1B4-436C-BBB4-850C2F1820F4}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{9697448F-645A-41FB-AA3F-4313B4171D87}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{C9647F5F-F163-4499-88A9-FE5C8EC41F54}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{446BD414-9F72-4680-85DB-437C59B7F4B8}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{6F0B7F15-88AA-41F1-9DA5-B98FEA05983C}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{81B547B6-D366-403A-9619-4AF2BA3D357E}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{CED7DB58-C036-457E-B16B-8854E9B5F833}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{36A3FE49-643E-4705-A8D6-4D93D9240FBF}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{9042E44F-04DD-4F14-81A9-59CFD3048EF1}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{8C3A3632-E15C-4D14-8907-13D02F034A09}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{7A18F385-6AA5-4D7A-8CEB-0DDEFECC343A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
